--- a/multi-agent-demo/docs/Confluent Sales Cloud Infor.xlsx
+++ b/multi-agent-demo/docs/Confluent Sales Cloud Infor.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,15 +460,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Contract Expiration Date</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Products</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Next Steps</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Agent Next Steps</t>
         </is>
@@ -494,23 +499,22 @@
         <v>1000000</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>45076</v>
-      </c>
-      <c r="F2" t="inlineStr">
+        <v>45077</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Cognos</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days.</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review the active IBM-Confluent contract portfolio and confirm which agreements are currently enabled for sales activity. | Prioritize contracts with renewal dates or notice windows in the next 30-90 days. | Update the CRM Agent Next Steps column with the highest-priority seller actions for Confluent.</t>
-        </is>
-      </c>
+          <t>Deal signed by CPO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -532,23 +536,22 @@
         <v>250000</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>45687</v>
-      </c>
-      <c r="F3" t="inlineStr">
+        <v>45688</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>watsonx Orchestrate, watsonx.governance, watsonx.ai</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days.</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review the active IBM-Confluent contract portfolio and confirm which agreements are currently enabled for sales activity. | Prioritize contracts with renewal dates or notice windows in the next 30-90 days. | Update the CRM Agent Next Steps column with the highest-priority seller actions for Confluent.</t>
-        </is>
-      </c>
+          <t>CFO signed 1 year renewals</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -570,23 +573,22 @@
         <v>250000</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>45321</v>
-      </c>
-      <c r="F4" t="inlineStr">
+        <v>45322</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>45688</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>watsonx Orchestrate, watsonx.governance, watsonx.ai</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days.</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review the active IBM-Confluent contract portfolio and confirm which agreements are currently enabled for sales activity. | Prioritize contracts with renewal dates or notice windows in the next 30-90 days. | Update the CRM Agent Next Steps column with the highest-priority seller actions for Confluent.</t>
-        </is>
-      </c>
+          <t>CFO signed 1 year deal for them embedding watsonx to add agentic and AI use cases to their solution</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -608,23 +610,22 @@
         <v>400000</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>45381</v>
-      </c>
-      <c r="F5" t="inlineStr">
+        <v>45504</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>watsonx.data</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days.</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review the active IBM-Confluent contract portfolio and confirm which agreements are currently enabled for sales activity. | Prioritize contracts with renewal dates or notice windows in the next 30-90 days. | Update the CRM Agent Next Steps column with the highest-priority seller actions for Confluent.</t>
-        </is>
-      </c>
+          <t>Expand to use watsonx.data for easy data access into LLM and Agents</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -648,21 +649,18 @@
       <c r="E6" s="2" t="n">
         <v>45361</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>watsonx.data</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days.</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review the active IBM-Confluent contract portfolio and confirm which agreements are currently enabled for sales activity. | Prioritize contracts with renewal dates or notice windows in the next 30-90 days. | Update the CRM Agent Next Steps column with the highest-priority seller actions for Confluent.</t>
-        </is>
-      </c>
+          <t>Did not want to go with the expansion</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -686,21 +684,18 @@
       <c r="E7" s="2" t="n">
         <v>415007</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>watsonx Orchestrate, watsonx.governance, watsonx.ai</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days.</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review the active IBM-Confluent contract portfolio and confirm which agreements are currently enabled for sales activity. | Prioritize contracts with renewal dates or notice windows in the next 30-90 days. | Update the CRM Agent Next Steps column with the highest-priority seller actions for Confluent.</t>
-        </is>
-      </c>
+          <t>watsonx ESA expired working with team on size needed to renew</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -724,17 +719,18 @@
       <c r="E8" s="2" t="n">
         <v>46173</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Apptio, Cloudability</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Meeting with CTO and CPO is discuss cloud optimization they can do with Apptio and Cloudability</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -758,17 +754,18 @@
       <c r="E9" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>watsonx Orchestrate</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Meeting with their CPO to discuss larger partnership at IBM Think post initial renewal</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -792,17 +789,18 @@
       <c r="E10" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Cognos</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>CPO Not ready to move forward yet</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -826,21 +824,18 @@
       <c r="E11" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Cognos</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days.</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review the active IBM-Confluent contract portfolio and confirm which agreements are currently enabled for sales activity. | Prioritize contracts with renewal dates or notice windows in the next 30-90 days. | Update the CRM Agent Next Steps column with the highest-priority seller actions for Confluent.</t>
-        </is>
-      </c>
+          <t>Quote for renewal being shared with team and discussing expansion</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -864,21 +859,18 @@
       <c r="E12" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>Cognos</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days.</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review the active IBM-Confluent contract portfolio and confirm which agreements are currently enabled for sales activity. | Prioritize contracts with renewal dates or notice windows in the next 30-90 days. | Update the CRM Agent Next Steps column with the highest-priority seller actions for Confluent.</t>
-        </is>
-      </c>
+          <t>Meeting with CPO to discuss possible expansion of Cognos on 4/1/2026</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -902,26 +894,23 @@
       <c r="E13" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>watsonx Orchestrate, watsonx.governance, watsonx.ai</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days.</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review the active IBM-Confluent contract portfolio and confirm which agreements are currently enabled for sales activity. | Prioritize contracts with renewal dates or notice windows in the next 30-90 days. | Update the CRM Agent Next Steps column with the highest-priority seller actions for Confluent.</t>
-        </is>
-      </c>
+          <t>Needed to delay renewal due to change in org structure</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Confluent - Contract Portfolio Review</t>
+          <t>Unknown - Seller Inquiry 2026-04-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -931,7 +920,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Renewal / Expansion Review</t>
+          <t>Seller Inquiry</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -940,26 +929,27 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>Portfolio Review</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days.</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review the active IBM-Confluent contract portfolio and confirm which agreements are currently enabled for sales activity. | Prioritize contracts with renewal dates or notice windows in the next 30-90 days. | Update the CRM Agent Next Steps column with the highest-priority seller actions for Confluent.</t>
+          <t>Prepare a renewal and expiration dashboard for Confluent with notice windows and owners.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Prepare a renewal and expiration dashboard for Confluent with notice windows and owners. | Review the active IBM-Confluent contract portfolio and confirm which agreements are currently enabled for sales activity. | Prioritize contracts with renewal dates or notice windows in the next 30-90 days. | Update the CRM Agent Next Steps column with the highest-priority seller actions for Confluent.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Confluent - Contract Portfolio Review</t>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -969,28 +959,809 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Renewal / Expansion Review</t>
+          <t>Seller Inquiry</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Portfolio Review</t>
-        </is>
-      </c>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
+          <t>watsonx.governance, watsonx.data, watsonx Orchestrate</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out. | Prepare a renewal and expiration dashboard for Confluent with notice windows and owners. | Meet with the account before renewal because Cognos is in the renewal scope for Confluent Cognos | Prepare renewal outreach for Confluent watsonx ESA | Prepare renewal outreach for Confluent watsonx ESA Renewal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Confluent IBM-1.30.2024, Confluent IBM-3.29.2024, watsonx, Cognos</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Review Confluent_IBM-1.30.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Review Confluent_IBM-1.30.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations. | Review Confluent_IBM-3.29.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations. | Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review active contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>watsonx.ai, watsonx.data, watsonx</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Prepare a renewal and expiration dashboard for Confluent with notice windows and owners.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Prepare a renewal and expiration dashboard for Confluent with notice windows and owners. | Meet with the account before renewal because Cognos is in the renewal scope for Confluent Cognos | Prepare renewal outreach for Confluent watsonx ESA | Prepare renewal outreach for Confluent watsonx ESA Renewal | Review the active IBM-Confluent contract portfolio and confirm which agreements are currently enabled for sales activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Confluent IBM-1.30.2024, Confluent IBM-3.29.2024, watsonx, Cognos</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Review Confluent_IBM-1.30.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Review Confluent_IBM-1.30.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations. | Review Confluent_IBM-3.29.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations. | Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review active contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>watsonx.ai, watsonx.data, Portfolio Review</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Prepare a renewal and expiration dashboard for Confluent with notice windows and owners.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Prepare a renewal and expiration dashboard for Confluent with notice windows and owners. | Meet with the account before renewal because Cognos is in the renewal scope for Confluent Cognos | Prepare renewal outreach for Confluent watsonx ESA | Prepare renewal outreach for Confluent watsonx ESA Renewal | Review the active IBM-Confluent contract portfolio and confirm which agreements are currently enabled for sales activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>watsonx.ai, watsonx.data, Portfolio Review</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out. | Prepare a renewal and expiration dashboard for Confluent with notice windows and owners. | Meet with the account before renewal because Cognos is in the renewal scope for Confluent Cognos | Prepare renewal outreach for Confluent watsonx ESA | Prepare renewal outreach for Confluent watsonx ESA Renewal</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>watsonx.ai, watsonx.data, Portfolio Review</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out. | Prepare a renewal and expiration dashboard for Confluent with notice windows and owners. | Meet with the account before renewal because Cognos is in the renewal scope for Confluent Cognos | Prepare renewal outreach for Confluent watsonx ESA | Prepare renewal outreach for Confluent watsonx ESA Renewal</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>watsonx.ai, watsonx.data, Portfolio Review</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>Schedule a portfolio review with the Confluent account team within the next 30 days.</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review the active IBM-Confluent contract portfolio and confirm which agreements are currently enabled for sales activity. | Prioritize contracts with renewal dates or notice windows in the next 30-90 days. | Update the CRM Agent Next Steps column with the highest-priority seller actions for Confluent.</t>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Meet with the account before renewal because Cognos is in the renewal scope for Confluent Cognos | Prepare renewal outreach for Confluent watsonx ESA | Prepare renewal outreach for Confluent watsonx ESA Renewal</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Confluent IBM-1.30.2024, Confluent IBM-3.29.2024, watsonx, Cognos</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Review Confluent_IBM-1.30.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Review Confluent_IBM-1.30.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations. | Review Confluent_IBM-3.29.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations. | Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review active contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>watsonx.ai, Cognos, watsonx.governance</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Prepare a renewal and expiration dashboard for Confluent with notice windows and owners.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Prepare a renewal and expiration dashboard for Confluent with notice windows and owners. | Meet with the account before renewal because Cognos is in the renewal scope for Confluent Cognos | Prepare renewal outreach for Confluent watsonx ESA | Prepare renewal outreach for Confluent watsonx ESA Renewal | Review the active IBM-Confluent contract portfolio and confirm which agreements are currently enabled for sales activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>watsonx.ai, Cognos, watsonx.governance</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out. | Prepare a renewal and expiration dashboard for Confluent with notice windows and owners. | Meet with the account before renewal because Cognos is in the renewal scope for Confluent Cognos | Prepare renewal outreach for Confluent watsonx ESA | Prepare renewal outreach for Confluent watsonx ESA Renewal</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Confluent IBM-1.30.2024, Confluent IBM-3.29.2024, watsonx, Cognos</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Review Confluent_IBM-1.30.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Review Confluent_IBM-1.30.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations. | Review Confluent_IBM-3.29.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations. | Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review active contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>watsonx.governance, Portfolio Review, watsonx.ai</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out. | Prepare a renewal and expiration dashboard for Confluent with notice windows and owners. | Meet with the account before renewal because Cognos is in the renewal scope for Confluent Cognos | Prepare renewal outreach for Confluent watsonx ESA | Prepare renewal outreach for Confluent watsonx ESA Renewal</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>watsonx.governance, Portfolio Review, watsonx.ai</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out. | Prepare a renewal and expiration dashboard for Confluent with notice windows and owners. | Meet with the account before renewal because Cognos is in the renewal scope for Confluent Cognos | Prepare renewal outreach for Confluent watsonx ESA | Prepare renewal outreach for Confluent watsonx ESA Renewal</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Confluent IBM-1.30.2024, Confluent IBM-3.29.2024, watsonx, Cognos</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Review Confluent_IBM-1.30.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Review Confluent_IBM-1.30.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations. | Review Confluent_IBM-3.29.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations. | Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review active contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>watsonx, watsonx.data, Cognos</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out. | Prepare a renewal and expiration dashboard for Confluent with notice windows and owners. | Meet with the account before renewal because Cognos is in the renewal scope for Confluent Cognos | Prepare renewal outreach for Confluent watsonx ESA | Prepare renewal outreach for Confluent watsonx ESA Renewal</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>watsonx, watsonx.data, Cognos</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out. | Prepare a renewal and expiration dashboard for Confluent with notice windows and owners. | Meet with the account before renewal because Cognos is in the renewal scope for Confluent Cognos | Prepare renewal outreach for Confluent watsonx ESA | Prepare renewal outreach for Confluent watsonx ESA Renewal</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Confluent IBM-1.30.2024, Confluent IBM-3.29.2024, watsonx, Cognos</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Review Confluent_IBM-1.30.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Review Confluent_IBM-1.30.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations. | Review Confluent_IBM-3.29.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations. | Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review active contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>watsonx.governance, watsonx, watsonx Orchestrate</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out. | Prepare a renewal and expiration dashboard for Confluent with notice windows and owners. | Meet with the account before renewal because Cognos is in the renewal scope for Confluent Cognos | Prepare renewal outreach for Confluent watsonx ESA | Prepare renewal outreach for Confluent watsonx ESA Renewal</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>watsonx.governance, watsonx, watsonx Orchestrate</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Review the recently expired contract Confluent_IBM-1.30.2025.docx and decide this week whether to renew, replace, or close it out. | Prepare a renewal and expiration dashboard for Confluent with notice windows and owners. | Meet with the account before renewal because Cognos is in the renewal scope for Confluent Cognos | Prepare renewal outreach for Confluent watsonx ESA | Prepare renewal outreach for Confluent watsonx ESA Renewal</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Confluent - Seller Inquiry 2026-04-08</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>IBM Seller</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Seller Inquiry</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Confluent IBM-1.30.2024, Confluent IBM-3.29.2024, watsonx, Cognos</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Review Confluent_IBM-1.30.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Review Confluent_IBM-1.30.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations. | Review Confluent_IBM-3.29.2024.docx this week to confirm active status, enabled permissions, and any outstanding obligations. | Schedule a portfolio review with the Confluent account team within the next 30 days. | Confirm whether any downstream SOW or enablement step is still required before additional co-sell activity. | Review active contracts</t>
         </is>
       </c>
     </row>

--- a/multi-agent-demo/docs/Confluent Sales Cloud Infor.xlsx
+++ b/multi-agent-demo/docs/Confluent Sales Cloud Infor.xlsx
@@ -616,7 +616,7 @@
         <v>7/31/26</v>
       </c>
       <c r="G9" t="str">
-        <v>watsonx Orchestrate</v>
+        <v>watsonx.data</v>
       </c>
       <c r="H9" t="str">
         <v>Meeting with their CPO to discuss larger partnership at IBM Think post initial renewal</v>
